--- a/data/4-22-26/NIST610 run 1.xlsx
+++ b/data/4-22-26/NIST610 run 1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://grinco-my.sharepoint.com/personal/sharpe_grinnell_edu/Documents/Documents/Archaelogy LA ICP MS/4_22_26/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B3ECBCA0-ACAF-48CB-8C02-F833B6B1C994}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{EDBD03B7-3798-425F-9136-96941FCF3237}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="24" yWindow="744" windowWidth="23016" windowHeight="12216" xr2:uid="{C19C254E-B53C-412F-A12A-20C9EAD07F15}"/>
+    <workbookView xWindow="24" yWindow="744" windowWidth="23016" windowHeight="12216" xr2:uid="{2DBA7549-2F25-467D-B384-9DCB25F37AD9}"/>
   </bookViews>
   <sheets>
     <sheet name="NIST610 run 1" sheetId="1" r:id="rId1"/>
@@ -20,12 +20,114 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
   <si>
-    <t>Intensity Vs Time</t>
+    <t xml:space="preserve">Time in Seconds </t>
   </si>
   <si>
-    <t xml:space="preserve"> Counts per Second</t>
+    <t>Na23</t>
+  </si>
+  <si>
+    <t>Mg25</t>
+  </si>
+  <si>
+    <t>Al27</t>
+  </si>
+  <si>
+    <t>Si29</t>
+  </si>
+  <si>
+    <t>P31</t>
+  </si>
+  <si>
+    <t>S34</t>
+  </si>
+  <si>
+    <t>K39</t>
+  </si>
+  <si>
+    <t>Ca43</t>
+  </si>
+  <si>
+    <t>Sc45</t>
+  </si>
+  <si>
+    <t>Ti47</t>
+  </si>
+  <si>
+    <t>V51</t>
+  </si>
+  <si>
+    <t>Cr53</t>
+  </si>
+  <si>
+    <t>Mn55</t>
+  </si>
+  <si>
+    <t>Fe57</t>
+  </si>
+  <si>
+    <t>Co59</t>
+  </si>
+  <si>
+    <t>Ni60</t>
+  </si>
+  <si>
+    <t>Cu63</t>
+  </si>
+  <si>
+    <t>Zn66</t>
+  </si>
+  <si>
+    <t>Rb85</t>
+  </si>
+  <si>
+    <t>Sr88</t>
+  </si>
+  <si>
+    <t>Zr90</t>
+  </si>
+  <si>
+    <t>Nb93</t>
+  </si>
+  <si>
+    <t>Mo98</t>
+  </si>
+  <si>
+    <t>Ag107</t>
+  </si>
+  <si>
+    <t>Sn118</t>
+  </si>
+  <si>
+    <t>Sb121</t>
+  </si>
+  <si>
+    <t>Cs133</t>
+  </si>
+  <si>
+    <t>Ba138</t>
+  </si>
+  <si>
+    <t>La139</t>
+  </si>
+  <si>
+    <t>Pr141</t>
+  </si>
+  <si>
+    <t>Hf180</t>
+  </si>
+  <si>
+    <t>Re187</t>
+  </si>
+  <si>
+    <t>Au197</t>
+  </si>
+  <si>
+    <t>Pb208</t>
+  </si>
+  <si>
+    <t>Bi209</t>
   </si>
 </sst>
 </file>
@@ -885,7 +987,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B5C12C9-E47E-4C4E-98DF-F6BA55E3892E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA48B088-2D89-455C-8638-1575074A8323}">
   <dimension ref="A1:AJ97"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
@@ -896,6 +998,108 @@
       <c r="B1" t="s">
         <v>1</v>
       </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AD1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>30</v>
+      </c>
+      <c r="AF1" t="s">
+        <v>31</v>
+      </c>
+      <c r="AG1" t="s">
+        <v>32</v>
+      </c>
+      <c r="AH1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AI1" t="s">
+        <v>34</v>
+      </c>
+      <c r="AJ1" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="3" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A3">
